--- a/labs/lab03_dora/amostra_ouro/rotulagem_salomao.xlsx
+++ b/labs/lab03_dora/amostra_ouro/rotulagem_salomao.xlsx
@@ -550,8 +550,16 @@
           <t>classification, coco, computer-vision, deep-learning, hacktoberfest, image-processing, instance-segmentation, low-code, machine-learning, metrics, object-detection, oriented-bounding-box, pascal-voc, python, pytorch, tensorflow, tracking, video-processing, yolo</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,8 +582,16 @@
           <t>ai, augmentation, flourishing, life, work</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -598,8 +614,16 @@
           <t>batch-processing, data-analytics, data-pipelines, data-processing, dataflow, etl, etl-framework, iot-analytics, kafka, machine-learning-algorithms, pathway, python, real-time, rust, stream-processing, streaming, time-series-analysis</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -622,8 +646,16 @@
           <t>ai, ai-agents, ai-crawler, ai-scraping, ai-search, crawler, data-extraction, html-to-markdown, llm, markdown, scraper, scraping, web-crawler, web-data, web-data-extraction, web-scraper, web-scraping, web-search, webscraping</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,8 +678,16 @@
           <t>cockroachdb, database, javascript, loggy-core, loggy-terminal, mariadb, mongodb, mssql, mysql, nodejs, orm, postgres, postgresql, prisma, prisma-client, query-builder, sql-server, sqlite, sqlserver, typescript</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,8 +710,16 @@
           <t>agentic-ai, agents, ai-memory, memory</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -690,8 +738,16 @@
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -714,8 +770,16 @@
           <t>agent, ai, anthropic, claude-code, compression, context-engineering, context-window, cursor, fastapi, langchain, llm, mcp, openai, prompt-engineering, proxy, python, rag, token-optimization, tokens, typescript</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,8 +798,16 @@
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -758,8 +830,16 @@
           <t>android, appwrite, backend, backend-as-a-service, docker, firebase, firewall, flutter, hosting, ios, javascript, nextjs, react, react-native, reactnative, self-hosted, selfhosted, supabase, swift, web</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -782,8 +862,16 @@
           <t>airflow, apache, apache-airflow, automation, dag, data-engineering, data-integration, data-orchestrator, data-pipelines, data-science, elt, etl, machine-learning, mlops, orchestration, python, scheduler, workflow, workflow-engine, workflow-orchestration</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -806,8 +894,16 @@
           <t>ai, ai-agents, ai-memory, anthropic, artificial-intelligence, chromadb, claude, claude-agent-sdk, claude-agents, claude-code, claude-code-plugin, claude-skills, embeddings, long-term-memory, mem0, memory-engine, openmemory, rag, sqlite, supermemory</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -830,8 +926,16 @@
           <t>agents, ai, api, audio-generation, decentralized, distributed, image-generation, libp2p, llama, llm, mamba, mcp, musicgen, object-detection, rerank, stable-diffusion, text-generation, tts</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -854,8 +958,16 @@
           <t>hacktoberfest, http-client, javascript, nodejs, promise</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -878,8 +990,16 @@
           <t>blogging, cms, ghost, javascript, journalism, nodejs, publishing, web-application</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -902,8 +1022,16 @@
           <t>agent-framework, ai-agent, ai-agents, chatbot, chatops, discord-bot, llm-agents, llms, local-llm, mcp, model-context-protocol, multi-agent, openai-compatible, openclaw, personal-ai-assistant, python, self-hosted, telegram-bot-ai-assistant, webui, workflow-automation</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -926,8 +1054,16 @@
           <t>animations, hacktoberfest, manim, math, python</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -950,8 +1086,16 @@
           <t>agent, automation, feed, feedgenerator, huginn, monitoring, notifications, rss, scraper, twitter, twitter-streaming, webscraping</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -974,8 +1118,16 @@
           <t>astro, blog, browser, components, hybrid, islands, node, server, static, static-site-generator, universal</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -998,8 +1150,16 @@
           <t>agents, ai, ai-agents, aiagentframework, llms</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1022,8 +1182,16 @@
           <t>agent, artificial-intelligence, chatgpt, claude-ai, cli, developer-tools, gpt, llm, openai</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,8 +1214,16 @@
           <t>agent-skills, ai-agent, ai-job-search, ats, career, career-ops, careerops, claude-code, cli, cover-letter, cv, interview-prep, job-application, job-hunting, job-search, latex, local-first, open-source, resume, terminal</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1070,8 +1246,16 @@
           <t>data-analysis, data-science, data-visualization, deep-learning, developer-tools, machine-learning, python, streamlit</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1094,8 +1278,16 @@
           <t>alternatives, csharp, customization, developer-tools, dotnet, file-manager, files, fluent, fluent-design, git, good-first-issue, power-user, productivity, utilities, winappsdk, windows, windows-10, windows-11, winui, xaml</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1118,8 +1310,16 @@
           <t>framework, hacktoberfest, javascript, javascript-framework, microservices, nest, nestjs, node, nodejs, nodejs-framework, typescript, typescript-framework, websockets</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1142,8 +1342,16 @@
           <t>ai, alternative, auth, database, deno, embeddings, example, firebase, nextjs, oauth2, pgvector, postgis, postgres, postgresql, postgrest, realtime, supabase, vectors, websockets</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1166,8 +1374,16 @@
           <t>component, component-library, components, css, css-components, css-framework, daisyui, design-system, design-systems, front-end, postcss, svelte, tailwind, tailwind-css, tailwindcss, ui-design, ui-framework, ui-kit, ui-library, ui-pattern</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1190,8 +1406,16 @@
           <t>ai-app-builder, docker, internal-applications, internal-project, internal-tool, internal-tools, javascript, kubernetes, low-code, low-code-development-platform, low-code-framework, no-code, nodejs, reactjs, self-hosted, typescript, web-development-tools, workflow-automation</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1214,8 +1438,16 @@
           <t>csr, framework, full-stack, hacktoberfest, hybrid, node, nuxt, server-rendering, ssg, ssr, static-site-generator, universal, vue</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1238,8 +1470,16 @@
           <t>aws, aws-dynamodb, aws-lambda, azure-functions, google-cloud-functions, microservice, serverless, serverless-architectures, serverless-framework</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1262,8 +1502,16 @@
           <t>agents, ai, ai-agents, anthropic, chatgpt, deepagents, enterprise, framework, gemini, generative-ai, langchain, langgraph, llm, multiagent, open-source, openai, pydantic, python, rag, typescript</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1286,8 +1534,16 @@
           <t>bash, fish, fish-prompt, fish-theme, oh-my-zsh, powershell, rust, shell-prompt, starship, zsh, zsh-prompt, zsh-theme</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1310,8 +1566,16 @@
           <t>compiler, language, rust</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1334,8 +1598,16 @@
           <t>ggml</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1358,8 +1630,16 @@
           <t>cloud, cloud-management, graph, infrastructure-as-code, terraform</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1382,8 +1662,16 @@
           <t>agentic-workflow, ai, ai-agents, ai-runtime, ai-sandboxes, code-execution, code-interpreter, developer-tools</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1406,8 +1694,16 @@
           <t>cli, downloader, python, sponsorblock, youtube-dl, youtube-downloader, yt-dlp</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1430,8 +1726,16 @@
           <t>disassembler, reverse-engineering, software-analysis</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1454,8 +1758,16 @@
           <t>deno, javascript, rust, typescript</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1478,8 +1790,16 @@
           <t>angular, components, design-systems, documentation, html, javascript, react, react-native, stories, storybook, styleguide, svelte, testing, typescript, ui, vite, vue, web-components, webpack, workshop</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1502,8 +1822,16 @@
           <t>agent-skills, ai-agents, architecture-diagram, claude-code, claude-skills, codex, coding-agents, deepseek-harness, developer-tools, diagrams, diagrams-as-code, dsh-plugin, flowchart, llm, mermaid, opencode, sequence-diagram, software-architecture, system-design, visualization</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1526,8 +1854,16 @@
           <t>packaging, python, resolver, uv</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1550,8 +1886,16 @@
           <t>agent-orchestration, ai-agents, ai-assistant, desktop, llm, local-first, mcp, personal-ai, privacy, rust, second-brain, tauri</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1574,8 +1918,16 @@
           <t>automation, chrome, chromium, e2e-testing, electron, end-to-end-testing, firefox, javascript, playwright, test, test-automation, testing, testing-tools, web, webkit</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1598,8 +1950,16 @@
           <t>diagrams, diagrams-as-code, documentation, flowchart, javascript, mindmap, typescript, uml-diagrams</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1622,8 +1982,16 @@
           <t>agent-infrastructure, ai-agent, ai-search, automation, bilibili, claude-code, cli, cursor, free-api, llm-tools, mcp, python, reddit-scraper, twitter-scraper, web-scraper, xiaohongshu, youtube-transcript</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1646,8 +2014,16 @@
           <t>agent-skills, agentic-skills, ai-agent-skills, ai-agents, ai-coding, ai-workflows, antigravity, antigravity-skills, claude-code, claude-code-skills, codex-cli, codex-skills, cursor, cursor-skills, developer-tools, gemini-cli, gemini-skills, kiro, mcp, skill-library</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1666,8 +2042,16 @@
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1690,8 +2074,16 @@
           <t>agentic-ai, agentic-framework, agentic-workflow, agents, ai-agents, ai-assistant, ai-skills, autonomous-agents, claude, codex, dsh-plugin, harness, mcp-server, multi-agent, multi-agent-systems, npm, skills, swarm, swarm-intelligence, typescript</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1714,8 +2106,16 @@
           <t>ech, fail2ban, http, hysteria2, mixed, mtproto, nodes, post-quantum, reality, shadowsocks, shadowsocks2022, tls, trojan, tun, tunnel, vless, vmess, wireguard, x25519, xhttp</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1738,8 +2138,16 @@
           <t>compiler, markup, typesetting, typst</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1762,8 +2170,16 @@
           <t>android, proxy, shadowsocks, socks5, trojan, v2fly, v2ray, vless, vmess, vpn, xray, xtls</t>
         </is>
       </c>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1786,8 +2202,16 @@
           <t>browser, editor, monaco-editor, typescript, vscode</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1810,8 +2234,16 @@
           <t>ai4science, chineseocr, document-parsing, document-translation, kie, ocr, paddleocr-vl, pdf-extractor-rag, pdf-parser, pdf2markdown, pp-ocr, pp-structure, rag</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1834,8 +2266,16 @@
           <t>javascript, material, material-components, material-design, material-theme, semantic, typescript, ui, ui-components, ui-design, ui-kit, ui-library, vue, vue-components, vue-material, vuejs, vuejs3, vuetify, vuetifyjs</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1858,8 +2298,16 @@
           <t>android, asyncio, cli, command-line, concurrency, cross-platform, developer-tools, file-explorer, file-manager, filesystem, linux, macos, neovim, productivity, rust, terminal, tui, vim, windows</t>
         </is>
       </c>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1882,8 +2330,16 @@
           <t>arm64, auto-install, bootable-usb, bsd, chromeos, iso-files, legacy, linux, multiboot, persistence, secure-boot, uefi, unattended, unix, usb, windows, x86, x86-64</t>
         </is>
       </c>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1906,8 +2362,16 @@
           <t>agentic-coding, ai-coding, anthropic, claude-code, cli, command-line-tool, cost-reduction, developer-tools, llm, open-source, productivity, rust, token-optimization</t>
         </is>
       </c>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1930,8 +2394,16 @@
           <t>browser, chrome, chrome-devtools, debugging, devtools, mcp, mcp-server, puppeteer</t>
         </is>
       </c>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1954,8 +2426,16 @@
           <t>ai-video-generator, content-creation, ffmpeg, instagram-reels, llm, python, short-video, subtitles, text-to-speech, tiktok, video-automation, video-workflow, workflow-automation, youtube-shorts</t>
         </is>
       </c>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2187,7 +2667,11 @@
 (+112 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2276,7 +2760,11 @@
 - Releasing supervision `0.29.1` (#2350)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2363,7 +2851,11 @@
 - releasing `0.30.2`</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2446,7 +2938,11 @@
 - releasing `0.30.3`</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2526,7 +3022,11 @@
 - releasing `0.30.5`</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2573,7 +3073,11 @@
 - chore(release): Update version to v1.4.422</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2621,7 +3125,11 @@
 - chore(release): Update version to v1.4.448</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2668,7 +3176,11 @@
 - chore(release): Update version to v1.4.462</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2727,7 +3239,11 @@
 - chore(release): Update version to v1.4.466</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2770,7 +3286,11 @@
 - chore(release): Update version to v1.4.477</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2879,7 +3399,11 @@
 (+2 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2979,7 +3503,11 @@
 - Pathway 0.28.0 Release</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3088,7 +3616,11 @@
 (+1 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3180,7 +3712,11 @@
 - Pathway 0.30.1 release</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3273,7 +3809,11 @@
 - Pathway 0.31.1 release</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3402,7 +3942,11 @@
 (+80 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3555,7 +4099,11 @@
 (+68 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3660,7 +4208,11 @@
 - fix(scrapeURL/fire-engine/checkStatus): pending state</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3795,7 +4347,11 @@
 (+310 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3917,7 +4473,11 @@
 (+189 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4035,7 +4595,11 @@
 - chore(deps): update engines to 6.17.0-16.c0aafc03b8ef6cdced8654b9a817999e02457d6a (#28232)</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4162,7 +4726,11 @@
 (+111 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4205,7 +4773,11 @@
 - fix: correct engine for cloudflare (#28934)</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4304,7 +4876,11 @@
 - chore: bump @prisma/dev to 0.24.3 (#29396)</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4431,7 +5007,11 @@
 (+237 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4499,7 +5079,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4576,7 +5160,11 @@
 - Release v0.1.1</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4690,7 +5278,11 @@
 - Release v0.4.0</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4793,7 +5385,11 @@
 - Release v0.5.4</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4924,7 +5520,11 @@
 (+39 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5019,7 +5619,11 @@
 - feat(daemon): add WebSocket heartbeat with HTTP fallback</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5105,7 +5709,11 @@
 - docs: update June 22 changelog (#4406)</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5144,7 +5752,11 @@
           <t>- fix(agents): defend AccessPicker against undefined invocation_targets (GH #4915) (#4924)</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5209,7 +5821,11 @@
 - docs(changelog): add v0.3.41 release notes (en/zh/ja/ko) (#5094)</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5331,7 +5947,11 @@
 - docs(changelog): add v0.4.31 release entry (2026-08-20) (MUL-6474) (#7314)</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5372,7 +5992,11 @@
 - Merge pull request #293 from chopratejas/rust-perf-tier1-gil-dashmap-single-serialize</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5413,7 +6037,11 @@
 - Merge pull request #322 from chopratejas/retire-query-echo</t>
         </is>
       </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5456,7 +6084,11 @@
 - Merge pull request #403 from chopratejas/realign-F2_2-policy-tuning</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5570,7 +6202,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5616,7 +6252,11 @@
 - fix(relevance): gate ONNX embedding backend behind AVX2 to avoid SIGILL (#1723) (#1765)</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5669,7 +6309,11 @@
 - release: v0.15.26</t>
         </is>
       </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5714,7 +6358,11 @@
 - release: v1.0.17</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5763,7 +6411,11 @@
 - release: v1.0.25</t>
         </is>
       </c>
-      <c r="H44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5804,7 +6456,11 @@
 - release: v1.0.34</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5866,7 +6522,11 @@
 - release: v1.1.58</t>
         </is>
       </c>
-      <c r="H46" s="3" t="n"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6002,7 +6662,11 @@
 (+2379 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6045,7 +6709,11 @@
 - chore: add 1.7.5 to CHANGES.md</t>
         </is>
       </c>
-      <c r="H48" s="3" t="n"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6113,7 +6781,11 @@
 - Merge pull request #12937 from appwrite/chore/1.9.6-release</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6242,7 +6914,11 @@
 (+269 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H50" s="3" t="n"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6370,7 +7046,11 @@
 (+121 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6522,7 +7202,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H52" s="3" t="n"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6663,7 +7347,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H53" s="3" t="n"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6781,7 +7469,11 @@
 (+99 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H54" s="3" t="n"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6911,7 +7603,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H55" s="3" t="n"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7038,7 +7734,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H56" s="3" t="n"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7119,7 +7819,11 @@
 - Bump version to 4.2.10 and fix Windows compatibility by removing hardcoded macOS path</t>
         </is>
       </c>
-      <c r="H57" s="3" t="n"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7165,7 +7869,11 @@
 - chore: Bump version to 6.1.0</t>
         </is>
       </c>
-      <c r="H58" s="3" t="n"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7214,7 +7922,11 @@
 - chore: bump version to 7.2.2</t>
         </is>
       </c>
-      <c r="H59" s="3" t="n"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7274,7 +7986,11 @@
 - chore: bump version to 8.5.7</t>
         </is>
       </c>
-      <c r="H60" s="3" t="n"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7333,7 +8049,11 @@
 - chore: bump version to 10.0.2</t>
         </is>
       </c>
-      <c r="H61" s="3" t="n"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7389,7 +8109,11 @@
 - perf(react-ui): code-split bundle, speed up coverage suite (#10042)</t>
         </is>
       </c>
-      <c r="H62" s="3" t="n"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7479,7 +8203,11 @@
 - chore: :arrow_up: Update ggml-org/whisper.cpp to `f24588a272ae8e23280d9c220536437164e6ed28` (#10078)</t>
         </is>
       </c>
-      <c r="H63" s="3" t="n"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7529,7 +8257,11 @@
 - chore: :arrow_up: Update mudler/parakeet.cpp to `30a307553f1965ceb38a1a922069a71e7dd67bf3` (#10092)</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7581,7 +8313,11 @@
 - chore(deps): bump actions/cache from 4 to 6 (#10704)</t>
         </is>
       </c>
-      <c r="H65" s="3" t="n"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7703,7 +8439,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H66" s="3" t="n"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7824,7 +8564,11 @@
 (+472 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H67" s="3" t="n"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7920,7 +8664,11 @@
 - chore(release): prepare release 1.14.0 (#10563)</t>
         </is>
       </c>
-      <c r="H68" s="3" t="n"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8048,7 +8796,11 @@
 (+686 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H69" s="3" t="n"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8175,7 +8927,11 @@
 (+756 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H70" s="3" t="n"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8283,7 +9039,11 @@
 (+20 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H71" s="3" t="n"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8324,7 +9084,11 @@
 - v6.10.2</t>
         </is>
       </c>
-      <c r="H72" s="3" t="n"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8392,7 +9156,11 @@
 - v6.19.4</t>
         </is>
       </c>
-      <c r="H73" s="3" t="n"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8476,7 +9244,11 @@
 - v6.38.0</t>
         </is>
       </c>
-      <c r="H74" s="3" t="n"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8582,7 +9354,11 @@
 (+116 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H75" s="3" t="n"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8687,7 +9463,11 @@
 (+203 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H76" s="3" t="n"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8760,7 +9540,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H77" s="3" t="n"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8887,7 +9671,11 @@
 (+30 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H78" s="3" t="n"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9007,7 +9795,11 @@
 (+166 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H79" s="3" t="n"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9114,7 +9906,11 @@
 (+199 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H80" s="3" t="n"/>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9223,7 +10019,11 @@
 (+338 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H81" s="3" t="n"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9350,7 +10150,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H82" s="3" t="n"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9433,7 +10237,11 @@
 - Prepare new release `v0.19.2` (#4528)</t>
         </is>
       </c>
-      <c r="H83" s="3" t="n"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9544,7 +10352,11 @@
 - fix: fix permission problem in python-publish workflow</t>
         </is>
       </c>
-      <c r="H84" s="3" t="n"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9618,7 +10430,11 @@
 - Prepare new release: `v0.20.1` (#4615)</t>
         </is>
       </c>
-      <c r="H85" s="3" t="n"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9769,7 +10585,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H86" s="3" t="n"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9878,7 +10698,11 @@
 (+607 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H87" s="3" t="n"/>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9956,7 +10780,11 @@
 - Update CHANGES.md</t>
         </is>
       </c>
-      <c r="H88" s="3" t="n"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10019,7 +10847,11 @@
 - Tag Docker images with the release version</t>
         </is>
       </c>
-      <c r="H89" s="3" t="n"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10099,7 +10931,11 @@
 - Update changes for v2026.09.21</t>
         </is>
       </c>
-      <c r="H90" s="3" t="n"/>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10154,7 +10990,11 @@
 - Add a guide to recent upgrade paths</t>
         </is>
       </c>
-      <c r="H91" s="3" t="n"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10194,7 +11034,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H92" s="3" t="n"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10233,7 +11077,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H93" s="3" t="n"/>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10274,7 +11122,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H94" s="3" t="n"/>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10314,7 +11166,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H95" s="3" t="n"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10358,7 +11214,11 @@
           <t>- chore: ignore fixture packages in changesets (#18033)</t>
         </is>
       </c>
-      <c r="H96" s="3" t="n"/>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10431,7 +11291,11 @@
 - chore: update crewAI and crewAI-tools dependencies to version 0.203.0 and 0.76.0 respectively (#3674)</t>
         </is>
       </c>
-      <c r="H97" s="3" t="n"/>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10480,7 +11344,11 @@
 - feat: bump versions to 1.2.1 (#3800)</t>
         </is>
       </c>
-      <c r="H98" s="3" t="n"/>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10541,7 +11409,11 @@
 - [docs-freeze] docs: snapshot and changelog for v1.15.12 (#6836)</t>
         </is>
       </c>
-      <c r="H99" s="3" t="n"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10635,7 +11507,11 @@
 - [docs-freeze] docs: snapshot and changelog for v1.15.18 (#7138)</t>
         </is>
       </c>
-      <c r="H100" s="3" t="n"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10721,7 +11597,11 @@
 - [docs-freeze] docs: snapshot and changelog for v1.15.19 (#7266)</t>
         </is>
       </c>
-      <c r="H101" s="3" t="n"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10834,7 +11714,11 @@
 (+26 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H102" s="3" t="n"/>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10959,7 +11843,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H103" s="3" t="n"/>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11056,7 +11944,11 @@
 - chore(main): release 1.7.0 (#16140)</t>
         </is>
       </c>
-      <c r="H104" s="3" t="n"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11193,7 +12085,11 @@
 (+27 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H105" s="3" t="n"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11270,7 +12166,11 @@
 - chore(main): release 1.23.0 (#17634)</t>
         </is>
       </c>
-      <c r="H106" s="3" t="n"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11381,7 +12281,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H107" s="3" t="n"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11494,7 +12398,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H108" s="3" t="n"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11541,7 +12449,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H109" s="3" t="n"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11659,7 +12571,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H110" s="3" t="n"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11712,7 +12628,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H111" s="3" t="n"/>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11843,7 +12763,11 @@
 (+97 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H112" s="3" t="n"/>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11977,7 +12901,11 @@
 (+121 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H113" s="3" t="n"/>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12109,7 +13037,11 @@
 (+166 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H114" s="3" t="n"/>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12242,7 +13174,11 @@
 (+56 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H115" s="3" t="n"/>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12375,7 +13311,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H116" s="3" t="n"/>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12482,7 +13422,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H117" s="3" t="n"/>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12558,7 +13502,11 @@
 - Build: v4.0.37</t>
         </is>
       </c>
-      <c r="H118" s="3" t="n"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12637,7 +13585,11 @@
 - Build: v4.1.3</t>
         </is>
       </c>
-      <c r="H119" s="3" t="n"/>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12730,7 +13682,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H120" s="3" t="n"/>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12793,7 +13749,11 @@
 - Build: v4.2.7</t>
         </is>
       </c>
-      <c r="H121" s="3" t="n"/>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12898,7 +13858,11 @@
 - chore(release): publish v11.1.11 release</t>
         </is>
       </c>
-      <c r="H122" s="3" t="n"/>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13019,7 +13983,11 @@
 (+54 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H123" s="3" t="n"/>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13160,7 +14128,11 @@
 (+158 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H124" s="3" t="n"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13277,7 +14249,11 @@
 (+399 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H125" s="3" t="n"/>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13332,7 +14308,11 @@
 - v11.2.6</t>
         </is>
       </c>
-      <c r="H126" s="3" t="n"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13468,7 +14448,11 @@
 (+2477 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H127" s="3" t="n"/>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13592,7 +14576,11 @@
 (+231 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H128" s="3" t="n"/>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13725,7 +14713,11 @@
 (+337 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H129" s="3" t="n"/>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13856,7 +14848,11 @@
 (+520 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H130" s="3" t="n"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13991,7 +14987,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H131" s="3" t="n"/>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14036,7 +15036,11 @@
 - chore(release): 5.1.31</t>
         </is>
       </c>
-      <c r="H132" s="3" t="n"/>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14082,7 +15086,11 @@
 - chore(release): 5.4.2</t>
         </is>
       </c>
-      <c r="H133" s="3" t="n"/>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14127,7 +15135,11 @@
 - chore(release): 5.5.11</t>
         </is>
       </c>
-      <c r="H134" s="3" t="n"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14181,7 +15193,11 @@
 - chore(release): 5.5.15</t>
         </is>
       </c>
-      <c r="H135" s="3" t="n"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14226,7 +15242,11 @@
 - chore(release): 5.5.23</t>
         </is>
       </c>
-      <c r="H136" s="3" t="n"/>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14278,7 +15298,11 @@
 - UI Fixes Platform (#14271)</t>
         </is>
       </c>
-      <c r="H137" s="3" t="n"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14321,7 +15345,11 @@
 - Fix: Canvas width changes between switching layout in Editor and Viewer when max width is not 100% (#15265)</t>
         </is>
       </c>
-      <c r="H138" s="3" t="n"/>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14385,7 +15413,11 @@
 - 🚀 chore: update submodules to latest lts-3.16 after auto-merge (#15699)</t>
         </is>
       </c>
-      <c r="H139" s="3" t="n"/>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14446,7 +15478,11 @@
 - Feature: Add QuickBooks Online marketplace plugin (#15903)</t>
         </is>
       </c>
-      <c r="H140" s="3" t="n"/>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14523,7 +15559,11 @@
 - 🚀 chore: update submodules to latest lts-3.16 after auto-merge (#18132)</t>
         </is>
       </c>
-      <c r="H141" s="3" t="n"/>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14681,7 +15721,11 @@
 (+2087 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H142" s="3" t="n"/>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14862,7 +15906,11 @@
 (+59 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H143" s="3" t="n"/>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15002,7 +16050,11 @@
 (+8492 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H144" s="3" t="n"/>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15118,7 +16170,11 @@
 (+8610 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H145" s="3" t="n"/>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15258,7 +16314,11 @@
 (+8983 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H146" s="3" t="n"/>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15303,7 +16363,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H147" s="3" t="n"/>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15357,7 +16421,11 @@
 - chore: release 4.29.3 (#13210)</t>
         </is>
       </c>
-      <c r="H148" s="3" t="n"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15400,7 +16468,11 @@
 - chore: release 4.29.4 (#13213)</t>
         </is>
       </c>
-      <c r="H149" s="3" t="n"/>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15473,7 +16545,11 @@
 - chore: release 4.31.1 (#13296)</t>
         </is>
       </c>
-      <c r="H150" s="3" t="n"/>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15554,7 +16630,11 @@
 - chore: release 4.34.0 (#13494)</t>
         </is>
       </c>
-      <c r="H151" s="3" t="n"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15659,7 +16739,11 @@
           <t>- feat(anthropic): add more anthropic middleware (#33510)</t>
         </is>
       </c>
-      <c r="H152" s="3" t="n"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15725,7 +16809,11 @@
           <t>- release(text-splitters): 1.0.0 (#33565)</t>
         </is>
       </c>
-      <c r="H153" s="3" t="n"/>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15806,7 +16894,11 @@
 - fix(anthropic): support output_config (#35036)</t>
         </is>
       </c>
-      <c r="H154" s="3" t="n"/>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15858,7 +16950,11 @@
 - release(anthropic): 1.4.4 (#37757)</t>
         </is>
       </c>
-      <c r="H155" s="3" t="n"/>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15907,7 +17003,11 @@
 - release(fireworks): 1.6.0 (#39810)</t>
         </is>
       </c>
-      <c r="H156" s="3" t="n"/>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16027,7 +17127,11 @@
 (+171 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H157" s="3" t="n"/>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16091,7 +17195,11 @@
 - chore(master): release 1.24.1 (#7122)</t>
         </is>
       </c>
-      <c r="H158" s="3" t="n"/>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16186,7 +17294,11 @@
 - chore(master): release 1.24.2 (#7155)</t>
         </is>
       </c>
-      <c r="H159" s="3" t="n"/>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16249,7 +17361,11 @@
 - chore(master): release 1.25.1 (#7445)</t>
         </is>
       </c>
-      <c r="H160" s="3" t="n"/>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16361,7 +17477,11 @@
 (+18 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H161" s="3" t="n"/>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16499,7 +17619,11 @@
 (+3579 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H162" s="3" t="n"/>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16637,7 +17761,11 @@
 (+3138 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H163" s="3" t="n"/>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16685,7 +17813,11 @@
 - Auto merge of #158331 - Mark-Simulacrum:stable-patch, r=Mark-Simulacrum</t>
         </is>
       </c>
-      <c r="H164" s="3" t="n"/>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16728,7 +17860,11 @@
 - Auto merge of #159288 - Mark-Simulacrum:stable-next, r=Mark-Simulacrum</t>
         </is>
       </c>
-      <c r="H165" s="3" t="n"/>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16864,7 +18000,11 @@
 (+3811 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H166" s="3" t="n"/>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16902,7 +18042,11 @@
           <t>- common: add LLAMA_LOG_FILE env var (#17609)</t>
         </is>
       </c>
-      <c r="H167" s="3" t="n"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16969,7 +18113,11 @@
           <t>- models : fix YaRN regression + consolidate logic (#18006)</t>
         </is>
       </c>
-      <c r="H168" s="3" t="n"/>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17047,7 +18195,11 @@
 - mtmd: refactor audio preprocessing (#17978)</t>
         </is>
       </c>
-      <c r="H169" s="3" t="n"/>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17113,7 +18265,11 @@
           <t>- jinja : attribute support for join, map and sort (#18883)</t>
         </is>
       </c>
-      <c r="H170" s="3" t="n"/>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17190,7 +18346,11 @@
           <t>- vendor : update cpp-httplib to 0.53.0 (#26821)</t>
         </is>
       </c>
-      <c r="H171" s="3" t="n"/>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17233,7 +18393,11 @@
 - Prepare before 1.13.4 release (#37772)</t>
         </is>
       </c>
-      <c r="H172" s="3" t="n"/>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17278,7 +18442,11 @@
 - Merge pull request #38209 from hashicorp/prepare/1.14.6</t>
         </is>
       </c>
-      <c r="H173" s="3" t="n"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17324,7 +18492,11 @@
 - Merge pull request #38260 from hashicorp/prepare/1.14.7</t>
         </is>
       </c>
-      <c r="H174" s="3" t="n"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17387,7 +18559,11 @@
 - Prepare before 1.15.1 release (#38509)</t>
         </is>
       </c>
-      <c r="H175" s="3" t="n"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17436,7 +18612,11 @@
 - Prepare before 1.15.9 release (#39043)</t>
         </is>
       </c>
-      <c r="H176" s="3" t="n"/>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17495,7 +18675,11 @@
 - chore(sdk-go): bump to v0.138.0 (#3579)</t>
         </is>
       </c>
-      <c r="H177" s="3" t="n"/>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -17558,7 +18742,11 @@
 - chore(sdk-go): bump to v0.147.0 (#3950)</t>
         </is>
       </c>
-      <c r="H178" s="3" t="n"/>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17644,7 +18832,11 @@
 - chore(sdk-go): bump to v0.157.0 (#4220)</t>
         </is>
       </c>
-      <c r="H179" s="3" t="n"/>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17721,7 +18913,11 @@
 - chore(sdk-go): bump to v0.158.0 (#4242)</t>
         </is>
       </c>
-      <c r="H180" s="3" t="n"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17794,7 +18990,11 @@
 - chore(sdk-go): bump to v0.174.0 (#4676)</t>
         </is>
       </c>
-      <c r="H181" s="3" t="n"/>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17868,7 +19068,11 @@
 - Release 2025.10.14</t>
         </is>
       </c>
-      <c r="H182" s="3" t="n"/>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17928,7 +19132,11 @@
 - Release 2026.01.31</t>
         </is>
       </c>
-      <c r="H183" s="3" t="n"/>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17990,7 +19198,11 @@
 - Release 2026.03.13</t>
         </is>
       </c>
-      <c r="H184" s="3" t="n"/>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -18108,7 +19320,11 @@
 (+5 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H185" s="3" t="n"/>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -18227,7 +19443,11 @@
 (+12 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H186" s="3" t="n"/>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18305,7 +19525,11 @@
 - GP-1 Updated ChangeHistory for 11.4.3 release</t>
         </is>
       </c>
-      <c r="H187" s="3" t="n"/>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18406,7 +19630,11 @@
 (+751 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H188" s="3" t="n"/>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18505,7 +19733,11 @@
 - GP-1 Updated Change History for Ghidra 12.0.4</t>
         </is>
       </c>
-      <c r="H189" s="3" t="n"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -18606,7 +19838,11 @@
 (+13 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H190" s="3" t="n"/>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18707,7 +19943,11 @@
 (+125 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H191" s="3" t="n"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18775,7 +20015,11 @@
 - 2.7.7 (#32835)</t>
         </is>
       </c>
-      <c r="H192" s="3" t="n"/>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18936,7 +20180,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H193" s="3" t="n"/>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -19098,7 +20346,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H194" s="3" t="n"/>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -19262,7 +20514,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H195" s="3" t="n"/>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -19416,7 +20672,11 @@
 - 2.9.1 (#35669)</t>
         </is>
       </c>
-      <c r="H196" s="3" t="n"/>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19464,7 +20724,11 @@
 - Bump version from "9.1.9" to "9.1.10" [skip ci]</t>
         </is>
       </c>
-      <c r="H197" s="3" t="n"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19514,7 +20778,11 @@
 - Bump version from "10.0.5" to "10.0.6" [skip ci]</t>
         </is>
       </c>
-      <c r="H198" s="3" t="n"/>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -19568,7 +20836,11 @@
 - Bump version from "10.1.6" to "10.1.7" [skip ci]</t>
         </is>
       </c>
-      <c r="H199" s="3" t="n"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -19625,7 +20897,11 @@
 - Bump version from "10.4.2" to "10.4.3" [skip ci]</t>
         </is>
       </c>
-      <c r="H200" s="3" t="n"/>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19675,7 +20951,11 @@
 - Bump version from "10.5.5" to "10.5.6" [skip ci]</t>
         </is>
       </c>
-      <c r="H201" s="3" t="n"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -19729,7 +21009,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H202" s="3" t="n"/>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -19784,7 +21068,11 @@
           <t>- v2.1: copy PNG to clipboard, 1x/2x/4x scale selector</t>
         </is>
       </c>
-      <c r="H203" s="3" t="n"/>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -19838,7 +21126,11 @@
           <t>- v2.3.1: audit-driven doc sync, canvas clamp, menu polish, print CSS</t>
         </is>
       </c>
-      <c r="H204" s="3" t="n"/>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -19877,7 +21169,11 @@
 - release: archify 2.8.0</t>
         </is>
       </c>
-      <c r="H205" s="3" t="n"/>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -19928,7 +21224,11 @@
 - release: prepare v2.11.0</t>
         </is>
       </c>
-      <c r="H206" s="3" t="n"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -20044,7 +21344,11 @@
 - Bump version to 0.11.0 (#18683)</t>
         </is>
       </c>
-      <c r="H207" s="3" t="n"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -20116,7 +21420,11 @@
 - Bump version to 0.11.10 (#19293)</t>
         </is>
       </c>
-      <c r="H208" s="3" t="n"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -20241,7 +21549,11 @@
 - Bump version to 0.11.21 (#19810)</t>
         </is>
       </c>
-      <c r="H209" s="3" t="n"/>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -20372,7 +21684,11 @@
 - Bump version to 0.11.22 (#19917)</t>
         </is>
       </c>
-      <c r="H210" s="3" t="n"/>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -20472,7 +21788,11 @@
 - Bump version to 0.12.5 (#21140)</t>
         </is>
       </c>
-      <c r="H211" s="3" t="n"/>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -20546,7 +21866,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H212" s="3" t="n"/>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -20597,7 +21921,11 @@
 - chore(release): v0.51.6</t>
         </is>
       </c>
-      <c r="H213" s="3" t="n"/>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -20635,7 +21963,11 @@
           <t>- chore(release): v0.52.7</t>
         </is>
       </c>
-      <c r="H214" s="3" t="n"/>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -20767,7 +22099,11 @@
 (+69 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H215" s="3" t="n"/>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -20860,7 +22196,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H216" s="3" t="n"/>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -20993,7 +22333,11 @@
 (+269 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H217" s="3" t="n"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21041,7 +22385,11 @@
 - cherry-pick(#39171): devops: add ubuntu-22.04-arm bot</t>
         </is>
       </c>
-      <c r="H218" s="3" t="n"/>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -21180,7 +22528,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H219" s="3" t="n"/>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21333,7 +22685,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H220" s="3" t="n"/>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -21382,7 +22738,11 @@
 - cherry-pick(#42043): docs: release notes for v1.62 Python, Java, and .NET (#42044)</t>
         </is>
       </c>
-      <c r="H221" s="3" t="n"/>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -21436,7 +22796,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H222" s="3" t="n"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -21501,7 +22865,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H223" s="3" t="n"/>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -21550,7 +22918,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H224" s="3" t="n"/>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -21600,7 +22972,11 @@
           <t>(sem commits)</t>
         </is>
       </c>
-      <c r="H225" s="3" t="n"/>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -21650,7 +23026,11 @@
 - Merge pull request #8267 from mermaid-js/changeset-release/master</t>
         </is>
       </c>
-      <c r="H226" s="3" t="n"/>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -21711,7 +23091,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H227" s="3" t="n"/>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -21799,7 +23183,11 @@
 - bump: v1.2.0</t>
         </is>
       </c>
-      <c r="H228" s="3" t="n"/>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -21884,7 +23272,11 @@
 - release: v1.3.0 (#70)</t>
         </is>
       </c>
-      <c r="H229" s="3" t="n"/>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -21959,7 +23351,11 @@
 - chore: bump version to 1.4.1 (#341)</t>
         </is>
       </c>
-      <c r="H230" s="3" t="n"/>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -22031,7 +23427,11 @@
 - chore: bump version to 1.4.2 (#349)</t>
         </is>
       </c>
-      <c r="H231" s="3" t="n"/>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -22079,7 +23479,11 @@
 - feat: add research-engineer skill from Tiger-Foxx (PR #9)</t>
         </is>
       </c>
-      <c r="H232" s="3" t="n"/>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -22168,7 +23572,11 @@
 - chore(release): sync lockfile version for 8.3.0</t>
         </is>
       </c>
-      <c r="H233" s="3" t="n"/>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22245,7 +23653,11 @@
 - chore: release v10.9.0</t>
         </is>
       </c>
-      <c r="H234" s="3" t="n"/>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22322,7 +23734,11 @@
 - chore: release v12.10.0</t>
         </is>
       </c>
-      <c r="H235" s="3" t="n"/>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -22391,7 +23807,11 @@
 - [skip pages] chore: synchronize canonical repository state</t>
         </is>
       </c>
-      <c r="H236" s="3" t="n"/>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22463,7 +23883,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H237" s="3" t="n"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -22513,7 +23937,11 @@
 - chore: bump version to 1.4.10, update CHANGELOG</t>
         </is>
       </c>
-      <c r="H238" s="3" t="n"/>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22553,7 +23981,11 @@
           <t>- fix: ensure import rewrites survive npm publish lifecycle</t>
         </is>
       </c>
-      <c r="H239" s="3" t="n"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -22678,7 +24110,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H240" s="3" t="n"/>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -22788,7 +24224,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H241" s="3" t="n"/>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -22927,7 +24367,11 @@
 - docs: update plugin count to 32 in both READMEs</t>
         </is>
       </c>
-      <c r="H242" s="3" t="n"/>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -22977,7 +24421,11 @@
 - v3.11.0 — router ADR-148/149 + cost-tracker observability + fleet audits (#2398)</t>
         </is>
       </c>
-      <c r="H243" s="3" t="n"/>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -23025,7 +24473,11 @@
 - chore(release): 3.21.1 → 3.22.0</t>
         </is>
       </c>
-      <c r="H244" s="3" t="n"/>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -23178,7 +24630,11 @@
 - Merge pull request #2824 from ruvnet/chore/stable-npm-release-workflow</t>
         </is>
       </c>
-      <c r="H245" s="3" t="n"/>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -23234,7 +24690,11 @@
 - chore(release): bump to 3.37.0 — proxy fixes + new config flags</t>
         </is>
       </c>
-      <c r="H246" s="3" t="n"/>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -23315,7 +24775,11 @@
 - Refactor TLS peer cert verification settings</t>
         </is>
       </c>
-      <c r="H247" s="3" t="n"/>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -23447,7 +24911,11 @@
 (+139 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H248" s="3" t="n"/>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -23582,7 +25050,11 @@
 (+7 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H249" s="3" t="n"/>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -23703,7 +25175,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H250" s="3" t="n"/>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -23815,7 +25291,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H251" s="3" t="n"/>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -23955,7 +25435,11 @@
 (+498 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H252" s="3" t="n"/>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -24079,7 +25563,11 @@
 - Version bump</t>
         </is>
       </c>
-      <c r="H253" s="3" t="n"/>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -24132,7 +25620,11 @@
 - Version bump</t>
         </is>
       </c>
-      <c r="H254" s="3" t="n"/>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -24285,7 +25777,11 @@
 (+641 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H255" s="3" t="n"/>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -24359,7 +25855,11 @@
 - Version bump</t>
         </is>
       </c>
-      <c r="H256" s="3" t="n"/>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -24404,7 +25904,11 @@
 - up 1.10.24</t>
         </is>
       </c>
-      <c r="H257" s="3" t="n"/>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -24449,7 +25953,11 @@
 - up 1.10.25</t>
         </is>
       </c>
-      <c r="H258" s="3" t="n"/>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -24497,7 +26005,11 @@
 - up 1.10.32</t>
         </is>
       </c>
-      <c r="H259" s="3" t="n"/>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -24552,7 +26064,11 @@
 - up 2.2.1</t>
         </is>
       </c>
-      <c r="H260" s="3" t="n"/>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -24612,7 +26128,11 @@
 - up 2.2.5</t>
         </is>
       </c>
-      <c r="H261" s="3" t="n"/>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -24679,7 +26199,11 @@
 - v0.54.0 (#5027)</t>
         </is>
       </c>
-      <c r="H262" s="3" t="n"/>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -24822,7 +26346,11 @@
 (+2 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H263" s="3" t="n"/>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -24864,7 +26392,11 @@
 - Fixes missing language exports (#5121)</t>
         </is>
       </c>
-      <c r="H264" s="3" t="n"/>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -25032,7 +26564,11 @@
 (+56 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H265" s="3" t="n"/>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -25150,7 +26686,11 @@
 - Merge pull request #5487 from microsoft/hediet/b/release-0.57.0</t>
         </is>
       </c>
-      <c r="H266" s="3" t="n"/>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -25225,7 +26765,11 @@
 - update release note about v3.3.0 (#16662)</t>
         </is>
       </c>
-      <c r="H267" s="3" t="n"/>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -25275,7 +26819,11 @@
 - merge main branch to release/3.3 branch (#16878)</t>
         </is>
       </c>
-      <c r="H268" s="3" t="n"/>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -25333,7 +26881,11 @@
 - [cherry-pick] #17739, #17743, #17779, #17881 (#17915)</t>
         </is>
       </c>
-      <c r="H269" s="3" t="n"/>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -25408,7 +26960,11 @@
 - Fix auto versioning (#18072)</t>
         </is>
       </c>
-      <c r="H270" s="3" t="n"/>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -25479,7 +27035,11 @@
 - [Feat] Support PP-OCRv6 (#18104)</t>
         </is>
       </c>
-      <c r="H271" s="3" t="n"/>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -25545,7 +27105,11 @@
 - chore(release): publish v3.10.4</t>
         </is>
       </c>
-      <c r="H272" s="3" t="n"/>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -25594,7 +27158,11 @@
 - chore(release): publish v3.10.9</t>
         </is>
       </c>
-      <c r="H273" s="3" t="n"/>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -25701,7 +27269,11 @@
 (+431 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H274" s="3" t="n"/>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -25801,7 +27373,11 @@
 (+43 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H275" s="3" t="n"/>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -25920,7 +27496,11 @@
 (+8 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H276" s="3" t="n"/>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -26018,7 +27598,11 @@
 (+136 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H277" s="3" t="n"/>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -26061,7 +27645,11 @@
 - chore: bump version to 26.1.4 (#3498)</t>
         </is>
       </c>
-      <c r="H278" s="3" t="n"/>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -26119,7 +27707,11 @@
 - chore: bump version to 26.1.22</t>
         </is>
       </c>
-      <c r="H279" s="3" t="n"/>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -26217,7 +27809,11 @@
 (+34 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H280" s="3" t="n"/>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -26281,7 +27877,11 @@
 - chore: bump version to 26.9.1 (#4314)</t>
         </is>
       </c>
-      <c r="H281" s="3" t="n"/>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -26336,7 +27936,11 @@
 - 1.1.08 release</t>
         </is>
       </c>
-      <c r="H282" s="3" t="n"/>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -26404,7 +28008,11 @@
 - 1.1.09 release</t>
         </is>
       </c>
-      <c r="H283" s="3" t="n"/>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -26457,7 +28065,11 @@
 - 1.1.13 release</t>
         </is>
       </c>
-      <c r="H284" s="3" t="n"/>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -26520,7 +28132,11 @@
 - 1.1.15 release</t>
         </is>
       </c>
-      <c r="H285" s="3" t="n"/>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -26593,7 +28209,11 @@
 - 1.1.16 release.</t>
         </is>
       </c>
-      <c r="H286" s="3" t="n"/>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -26632,7 +28252,11 @@
           <t>(primeira release: sem release anterior para comparar)</t>
         </is>
       </c>
-      <c r="H287" s="3" t="n"/>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -26683,7 +28307,11 @@
 - Merge pull request #50 from rtk-ai/release-please--branches--master--components--rtk</t>
         </is>
       </c>
-      <c r="H288" s="3" t="n"/>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -26727,7 +28355,11 @@
 - Merge pull request #76 from rtk-ai/release-please--branches--master--components--rtk</t>
         </is>
       </c>
-      <c r="H289" s="3" t="n"/>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -26834,7 +28466,11 @@
 - Merge pull request #1878 from rtk-ai/release-please--branches--master--components--rtk</t>
         </is>
       </c>
-      <c r="H290" s="3" t="n"/>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -26888,7 +28524,11 @@
 - Merge pull request #3358 from rtk-ai/release-please--branches--master--components--rtk</t>
         </is>
       </c>
-      <c r="H291" s="3" t="n"/>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -26983,7 +28623,11 @@
 - chore(main): release chrome-devtools-mcp 0.13.0 (#678)</t>
         </is>
       </c>
-      <c r="H292" s="3" t="n"/>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -27042,7 +28686,11 @@
 - chore(main): release chrome-devtools-mcp 0.16.0 (#877)</t>
         </is>
       </c>
-      <c r="H293" s="3" t="n"/>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -27159,7 +28807,11 @@
 (+12 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H294" s="3" t="n"/>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -27276,7 +28928,11 @@
 (+13 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H295" s="3" t="n"/>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -27393,7 +29049,11 @@
 [... texto cortado; veja o link]</t>
         </is>
       </c>
-      <c r="H296" s="3" t="n"/>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -27511,7 +29171,11 @@
 (+24 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H297" s="3" t="n"/>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -27582,7 +29246,11 @@
 - Bump version to 1.2.9</t>
         </is>
       </c>
-      <c r="H298" s="3" t="n"/>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -27657,7 +29325,11 @@
 - feat: modernize WebUI and generation workflows</t>
         </is>
       </c>
-      <c r="H299" s="3" t="n"/>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -27795,7 +29467,11 @@
 (+21 commits; veja o link)</t>
         </is>
       </c>
-      <c r="H300" s="3" t="n"/>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -27918,7 +29594,11 @@
 - chore: bump version to 1.3.7</t>
         </is>
       </c>
-      <c r="H301" s="3" t="n"/>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
